--- a/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
@@ -2,8 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="요구사항 원장" sheetId="1" r:id="rId1"/>
-    <sheet name="기능(AS-IS) 원장" sheetId="2" r:id="rId2"/>
+    <sheet name="문서정보" sheetId="1" r:id="rId1"/>
+    <sheet name="요구사항 원장" sheetId="2" r:id="rId2"/>
+    <sheet name="기능(AS-IS) 원장" sheetId="3" r:id="rId3"/>
+    <sheet name="커버리지 현황" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +60,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>문서명</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>요구사항 추적표(RTM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>방법론</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rtm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>소스 커밋</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[미확인]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>작성자 / 버전 / 작성일</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[미확인] — 제출 전 사람이 채움</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>본 파일의 지위</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>정적 스캔 스냅샷(원천 데이터) — 대시보드에서의 확정 편집은 반영되지 않음. 최신화는 /understand-docs 재실행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>신뢰도 표기</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[확정]=정적 분석 근거(file:line) 보유, [추정]=추론, [미확인]=사람 채움 대상 — 사람 검수/사인오프 여부와 무관.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
@@ -68,6 +166,7 @@
     <col min="8" max="8" width="9" customWidth="1"/>
     <col min="9" max="9" width="32" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -121,6 +220,11 @@
           <t>수용기준 수</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>검수</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -163,6 +267,11 @@
       <c r="J2">
         <v>6</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>미검수</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -205,12 +314,18 @@
       <c r="J3">
         <v>6</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>미검수</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -218,9 +333,10 @@
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="54" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -251,15 +367,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>시험</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>연관 요구</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>근거</t>
         </is>
@@ -293,15 +414,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>CHANGED</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>REQ-001, REQ-002</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:149</t>
         </is>
@@ -335,11 +461,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G3"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:137</t>
         </is>
@@ -373,11 +504,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G4"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:128</t>
         </is>
@@ -411,15 +547,20 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>CHANGED</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>REQ-001, REQ-002</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:115</t>
         </is>
@@ -453,11 +594,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G6"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:106</t>
         </is>
@@ -491,11 +637,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G7"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:184</t>
         </is>
@@ -529,15 +680,20 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>CHANGED</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>REQ-001, REQ-002</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:159</t>
         </is>
@@ -571,15 +727,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>REQ-002</t>
         </is>
       </c>
-      <c r="H9"/>
+      <c r="I9"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -609,15 +770,20 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>REQ-002</t>
         </is>
       </c>
-      <c r="H10"/>
+      <c r="I10"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -647,15 +813,20 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>REQ-002</t>
         </is>
       </c>
-      <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -685,15 +856,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>REQ-001</t>
         </is>
       </c>
-      <c r="H12"/>
+      <c r="I12"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -723,15 +899,20 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>REQ-001</t>
         </is>
       </c>
-      <c r="H13"/>
+      <c r="I13"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -761,15 +942,20 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>REQ-001</t>
         </is>
       </c>
-      <c r="H14"/>
+      <c r="I14"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -799,11 +985,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G15"/>
-      <c r="H15" t="inlineStr">
+      <c r="H15"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:68</t>
         </is>
@@ -837,11 +1028,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G16"/>
-      <c r="H16" t="inlineStr">
+      <c r="H16"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:141</t>
         </is>
@@ -875,11 +1071,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G17"/>
-      <c r="H17" t="inlineStr">
+      <c r="H17"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:94</t>
         </is>
@@ -913,11 +1114,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G18"/>
-      <c r="H18" t="inlineStr">
+      <c r="H18"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:116</t>
         </is>
@@ -951,11 +1157,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G19"/>
-      <c r="H19" t="inlineStr">
+      <c r="H19"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:137</t>
         </is>
@@ -989,11 +1200,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G20"/>
-      <c r="H20" t="inlineStr">
+      <c r="H20"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:143</t>
         </is>
@@ -1027,11 +1243,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G21"/>
-      <c r="H21" t="inlineStr">
+      <c r="H21"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:190</t>
         </is>
@@ -1065,11 +1286,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G22"/>
-      <c r="H22" t="inlineStr">
+      <c r="H22"/>
+      <c r="I22" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:153</t>
         </is>
@@ -1103,11 +1329,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G23"/>
-      <c r="H23" t="inlineStr">
+      <c r="H23"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:179</t>
         </is>
@@ -1141,11 +1372,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G24"/>
-      <c r="H24" t="inlineStr">
+      <c r="H24"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:166</t>
         </is>
@@ -1179,11 +1415,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G25"/>
-      <c r="H25" t="inlineStr">
+      <c r="H25"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:107</t>
         </is>
@@ -1217,11 +1458,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G26"/>
-      <c r="H26" t="inlineStr">
+      <c r="H26"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:142</t>
         </is>
@@ -1255,11 +1501,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G27"/>
-      <c r="H27" t="inlineStr">
+      <c r="H27"/>
+      <c r="I27" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:119</t>
         </is>
@@ -1293,11 +1544,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G28"/>
-      <c r="H28" t="inlineStr">
+      <c r="H28"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:171</t>
         </is>
@@ -1331,16 +1587,345 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>미시험</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="G29"/>
-      <c r="H29" t="inlineStr">
+      <c r="H29"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>src/main/webapp/WEB-INF/web.xml:60</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I29"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>requirements</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>requirements</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>requirements</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>requirements</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>signedOff</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>requirements</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>byLifecycle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{"RECEIVED":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>planned</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>orphaned</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>functions</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tests</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tests</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tests</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tests</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>untested</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>gaps</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>unimplemented</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>REQ-001, REQ-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>gaps</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>orphanCode</t>
+        </is>
+      </c>
+      <c r="C17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>gaps</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>flow:ANY *.action, flow:ANY /actions/Account.action, flow:ANY /actions/Account.action?editAccount, flow:ANY /actions/Account.action?editAccountForm, flow:ANY /actions/Account.action?newAccount, flow:ANY /actions/Account.action?newAccountForm, flow:ANY /actions/Account.action?signoff, flow:ANY /actions/Account.action?signon, flow:ANY /actions/Cart.action?addItemToCart, flow:ANY /actions/Cart.action?checkOut, flow:ANY /actions/Cart.action?removeItemFromCart, flow:ANY /actions/Cart.action?updateCartQuantities, flow:ANY /actions/Cart.action?viewCart, flow:ANY /actions/Catalog.action, flow:ANY /actions/Catalog.action?searchProducts, flow:ANY /actions/Catalog.action?viewCategory, flow:ANY /actions/Catalog.action?viewItem, flow:ANY /actions/Catalog.action?viewProduct, flow:ANY /actions/Order.action?listOrders, flow:ANY /actions/Order.action?newOrder, flow:ANY /actions/Order.action?newOrderForm, flow:ANY /actions/Order.action?viewOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>byRequirement</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{"targetsTotal":6,"targetsBuilt":3,"acsTotal":6,"acsPassed":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>byRequirement</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{"targetsTotal":6,"targetsBuilt":3,"acsTotal":6,"acsPassed":0}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C20"/>
 </worksheet>
 </file>
--- a/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
@@ -5,7 +5,8 @@
     <sheet name="문서정보" sheetId="1" r:id="rId1"/>
     <sheet name="요구사항 원장" sheetId="2" r:id="rId2"/>
     <sheet name="기능(AS-IS) 원장" sheetId="3" r:id="rId3"/>
-    <sheet name="커버리지 현황" sheetId="4" r:id="rId4"/>
+    <sheet name="테스트 시나리오" sheetId="4" r:id="rId4"/>
+    <sheet name="커버리지 현황" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -331,7 +332,7 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="41" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="54" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
@@ -404,7 +405,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AccountActionBean#signonForm</t>
+          <t>ANY /actions/Account.action</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -451,7 +452,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AccountActionBean#editAccount</t>
+          <t>ANY /actions/Account.action?editAccount</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -494,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AccountActionBean#editAccountForm</t>
+          <t>ANY /actions/Account.action?editAccountForm</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -537,7 +538,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AccountActionBean#newAccount</t>
+          <t>ANY /actions/Account.action?newAccount</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,7 +585,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AccountActionBean#newAccountForm</t>
+          <t>ANY /actions/Account.action?newAccountForm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -627,7 +628,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AccountActionBean#signoff</t>
+          <t>ANY /actions/Account.action?signoff</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -670,7 +671,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AccountActionBean#signon</t>
+          <t>ANY /actions/Account.action?signon</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -975,7 +976,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CartActionBean#addItemToCart</t>
+          <t>ANY /actions/Cart.action?addItemToCart</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1018,7 +1019,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CartActionBean#checkOut</t>
+          <t>ANY /actions/Cart.action?checkOut</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1061,7 +1062,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CartActionBean#removeItemFromCart</t>
+          <t>ANY /actions/Cart.action?removeItemFromCart</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1104,7 +1105,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CartActionBean#updateCartQuantities</t>
+          <t>ANY /actions/Cart.action?updateCartQuantities</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1147,7 +1148,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CartActionBean#viewCart</t>
+          <t>ANY /actions/Cart.action?viewCart</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1190,7 +1191,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CatalogActionBean#viewMain</t>
+          <t>ANY /actions/Catalog.action</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1233,7 +1234,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CatalogActionBean#searchProducts</t>
+          <t>ANY /actions/Catalog.action?searchProducts</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1276,7 +1277,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CatalogActionBean#viewCategory</t>
+          <t>ANY /actions/Catalog.action?viewCategory</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1319,7 +1320,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CatalogActionBean#viewItem</t>
+          <t>ANY /actions/Catalog.action?viewItem</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1362,7 +1363,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CatalogActionBean#viewProduct</t>
+          <t>ANY /actions/Catalog.action?viewProduct</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1405,7 +1406,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>OrderActionBean#listOrders</t>
+          <t>ANY /actions/Order.action?listOrders</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1448,7 +1449,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OrderActionBean#newOrder</t>
+          <t>ANY /actions/Order.action?newOrder</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1491,7 +1492,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OrderActionBean#newOrderForm</t>
+          <t>ANY /actions/Order.action?newOrderForm</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OrderActionBean#viewOrder</t>
+          <t>ANY /actions/Order.action?viewOrder</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1577,7 +1578,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>net.sourceforge.stripes.controller.DispatcherServlet</t>
+          <t>ANY *.action</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1608,6 +1609,4816 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="9" max="9" width="56" customWidth="1"/>
+    <col min="10" max="10" width="60" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
+    <col min="13" max="13" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TS_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FN_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>기능명</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>요구ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Given</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Then</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TS-FN-001-N1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FN-001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>계정 기본 진입(로그인 폼)</t>
+        </is>
+      </c>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>계정 기본 진입(로그인 폼) 정상 처리</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action` 호출</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L2"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:149</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TS-FN-001-E1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FN-001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>계정 기본 진입(로그인 폼)</t>
+        </is>
+      </c>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>계정 기본 진입(로그인 폼) 예외 처리</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action` 호출</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:149</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TS-FN-001-B1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FN-001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>계정 기본 진입(로그인 폼)</t>
+        </is>
+      </c>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>계정 기본 진입(로그인 폼) 경계 조건</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action` 호출</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:149</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TS-FN-002-N1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FN-002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>계정 수정 처리</t>
+        </is>
+      </c>
+      <c r="D5"/>
+      <c r="E5"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>계정 수정 처리 정상 처리</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?editAccount` 호출</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L5"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:137</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TS-FN-002-E1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FN-002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>계정 수정 처리</t>
+        </is>
+      </c>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>계정 수정 처리 예외 처리</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?editAccount` 호출</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:137</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TS-FN-002-B1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FN-002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>계정 수정 처리</t>
+        </is>
+      </c>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>계정 수정 처리 경계 조건</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?editAccount` 호출</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L7"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:137</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TS-FN-003-N1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FN-003</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>계정 수정 폼</t>
+        </is>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>계정 수정 폼 정상 처리</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?editAccountForm` 호출</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L8"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:128</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TS-FN-003-E1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FN-003</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>계정 수정 폼</t>
+        </is>
+      </c>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>계정 수정 폼 예외 처리</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?editAccountForm` 호출</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:128</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TS-FN-003-B1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FN-003</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>계정 수정 폼</t>
+        </is>
+      </c>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>계정 수정 폼 경계 조건</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?editAccountForm` 호출</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:128</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TS-FN-004-N1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FN-004</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 처리</t>
+        </is>
+      </c>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 처리 정상 처리</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?newAccount` 호출</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L11"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:115</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TS-FN-004-E1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FN-004</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 처리</t>
+        </is>
+      </c>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 처리 예외 처리</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?newAccount` 호출</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:115</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TS-FN-004-B1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FN-004</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 처리</t>
+        </is>
+      </c>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 처리 경계 조건</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?newAccount` 호출</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L13"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:115</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TS-FN-005-N1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>FN-005</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 폼</t>
+        </is>
+      </c>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 폼 정상 처리</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?newAccountForm` 호출</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L14"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:106</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TS-FN-005-E1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FN-005</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 폼</t>
+        </is>
+      </c>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 폼 예외 처리</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?newAccountForm` 호출</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:106</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TS-FN-005-B1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FN-005</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 폼</t>
+        </is>
+      </c>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>신규 계정 등록 폼 경계 조건</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?newAccountForm` 호출</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:106</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TS-FN-006-N1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FN-006</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>로그아웃</t>
+        </is>
+      </c>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>로그아웃 정상 처리</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?signoff` 호출</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L17"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:184</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TS-FN-006-E1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FN-006</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>로그아웃</t>
+        </is>
+      </c>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>로그아웃 예외 처리</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?signoff` 호출</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:184</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TS-FN-006-B1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FN-006</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>로그아웃</t>
+        </is>
+      </c>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>로그아웃 경계 조건</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?signoff` 호출</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:184</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TS-FN-007-N1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FN-007</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>로그인 처리</t>
+        </is>
+      </c>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>로그인 처리 정상 처리</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?signon` 호출</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L20"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:159</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TS-FN-007-E1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FN-007</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>로그인 처리</t>
+        </is>
+      </c>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>로그인 처리 예외 처리</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?signon` 호출</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:159</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TS-FN-007-B1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>FN-007</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>로그인 처리</t>
+        </is>
+      </c>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>로그인 처리 경계 조건</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Account.action?signon` 호출</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L22"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/AccountActionBean.java:159</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TS-FN-028-N1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FN-028</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>네이버 계정 연동/자동가입</t>
+        </is>
+      </c>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>네이버 계정 연동/자동가입 정상 처리</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>`(제안) AccountActionBean#naverCallback 내부 분기` 호출</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: (제안) OAUTH_ACCOUNT(C) · ACCOUNT(CR) · SIGNON(CR)</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L23"/>
+      <c r="M23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TS-FN-028-E1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FN-028</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>네이버 계정 연동/자동가입</t>
+        </is>
+      </c>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>네이버 계정 연동/자동가입 예외 처리</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>`(제안) AccountActionBean#naverCallback 내부 분기` 호출</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M24"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TS-FN-028-B1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FN-028</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>네이버 계정 연동/자동가입</t>
+        </is>
+      </c>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>네이버 계정 연동/자동가입 경계 조건</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): (제안) OAUTH_ACCOUNT(C) · ACCOUNT(CR) · SIGNON(CR)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>`(제안) AccountActionBean#naverCallback 내부 분기` 호출</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L25"/>
+      <c r="M25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TS-FN-026-N1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FN-026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>네이버 로그인 진입(인가요청 리다이렉트)</t>
+        </is>
+      </c>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>네이버 로그인 진입(인가요청 리다이렉트) 정상 처리</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?naverLogin` 호출</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L26"/>
+      <c r="M26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TS-FN-026-E1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FN-026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>네이버 로그인 진입(인가요청 리다이렉트)</t>
+        </is>
+      </c>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>네이버 로그인 진입(인가요청 리다이렉트) 예외 처리</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?naverLogin` 호출</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TS-FN-026-B1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FN-026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>네이버 로그인 진입(인가요청 리다이렉트)</t>
+        </is>
+      </c>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>네이버 로그인 진입(인가요청 리다이렉트) 경계 조건</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?naverLogin` 호출</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TS-FN-027-N1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FN-027</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>네이버 OAuth 콜백 처리(토큰교환·프로필조회)</t>
+        </is>
+      </c>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>네이버 OAuth 콜백 처리(토큰교환·프로필조회) 정상 처리</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?naverCallback` 호출</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: (제안) — (네이버 토큰·사용자 외부 API)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L29"/>
+      <c r="M29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TS-FN-027-E1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FN-027</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>네이버 OAuth 콜백 처리(토큰교환·프로필조회)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>REQ-002</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AC-4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>네이버 OAuth 콜백 처리(토큰교환·프로필조회) 예외 처리 1</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>예외 조건 성립: state 불일치 또는 토큰 교환 실패 시 로그인을 거부하고 에러를 처리한다</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?naverCallback` 호출</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + AC 기준의 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L30"/>
+      <c r="M30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TS-FN-027-B1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FN-027</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>네이버 OAuth 콜백 처리(토큰교환·프로필조회)</t>
+        </is>
+      </c>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>네이버 OAuth 콜백 처리(토큰교환·프로필조회) 경계 조건</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): (제안) — (네이버 토큰·사용자 외부 API)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?naverCallback` 호출</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L31"/>
+      <c r="M31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TS-FN-025-N1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FN-025</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>카카오 계정 연동/자동가입</t>
+        </is>
+      </c>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>카카오 계정 연동/자동가입 정상 처리</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>`(제안) AccountActionBean#kakaoCallback 내부 분기` 호출</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: (제안) OAUTH_ACCOUNT(C) · ACCOUNT(CR) · SIGNON(CR)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L32"/>
+      <c r="M32"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TS-FN-025-E1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FN-025</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>카카오 계정 연동/자동가입</t>
+        </is>
+      </c>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>카카오 계정 연동/자동가입 예외 처리</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>`(제안) AccountActionBean#kakaoCallback 내부 분기` 호출</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TS-FN-025-B1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FN-025</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>카카오 계정 연동/자동가입</t>
+        </is>
+      </c>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>카카오 계정 연동/자동가입 경계 조건</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): (제안) OAUTH_ACCOUNT(C) · ACCOUNT(CR) · SIGNON(CR)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>`(제안) AccountActionBean#kakaoCallback 내부 분기` 호출</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L34"/>
+      <c r="M34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TS-FN-023-N1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FN-023</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>카카오 로그인 진입(인가요청 리다이렉트)</t>
+        </is>
+      </c>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>카카오 로그인 진입(인가요청 리다이렉트) 정상 처리</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?kakaoLogin` 호출</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L35"/>
+      <c r="M35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TS-FN-023-E1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FN-023</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>카카오 로그인 진입(인가요청 리다이렉트)</t>
+        </is>
+      </c>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>카카오 로그인 진입(인가요청 리다이렉트) 예외 처리</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?kakaoLogin` 호출</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TS-FN-023-B1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FN-023</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>카카오 로그인 진입(인가요청 리다이렉트)</t>
+        </is>
+      </c>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>카카오 로그인 진입(인가요청 리다이렉트) 경계 조건</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?kakaoLogin` 호출</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TS-FN-024-N1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FN-024</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>카카오 OAuth 콜백 처리(토큰교환·프로필조회)</t>
+        </is>
+      </c>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>카카오 OAuth 콜백 처리(토큰교환·프로필조회) 정상 처리</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?kakaoCallback` 호출</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: (제안) — (카카오 토큰·사용자 외부 API)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L38"/>
+      <c r="M38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TS-FN-024-E1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FN-024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>카카오 OAuth 콜백 처리(토큰교환·프로필조회)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AC-4</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>카카오 OAuth 콜백 처리(토큰교환·프로필조회) 예외 처리 1</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>예외 조건 성립: state 불일치 또는 토큰 교환 실패 시 로그인을 거부하고 에러를 처리한다</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?kakaoCallback` 호출</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + AC 기준의 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L39"/>
+      <c r="M39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TS-FN-024-B1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FN-024</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>카카오 OAuth 콜백 처리(토큰교환·프로필조회)</t>
+        </is>
+      </c>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>카카오 OAuth 콜백 처리(토큰교환·프로필조회) 경계 조건</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): (제안) — (카카오 토큰·사용자 외부 API)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>`(제안) GET /actions/Account.action?kakaoCallback` 호출</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L40"/>
+      <c r="M40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TS-FN-008-N1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FN-008</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>장바구니에 품목 담기</t>
+        </is>
+      </c>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>장바구니에 품목 담기 정상 처리</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?addItemToCart` 호출</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L41"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:68</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TS-FN-008-E1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FN-008</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>장바구니에 품목 담기</t>
+        </is>
+      </c>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>장바구니에 품목 담기 예외 처리</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?addItemToCart` 호출</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:68</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TS-FN-008-B1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FN-008</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>장바구니에 품목 담기</t>
+        </is>
+      </c>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>장바구니에 품목 담기 경계 조건</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?addItemToCart` 호출</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L43"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:68</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TS-FN-009-N1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FN-009</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>체크아웃 진입</t>
+        </is>
+      </c>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>체크아웃 진입 정상 처리</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?checkOut` 호출</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L44"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:141</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TS-FN-009-E1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FN-009</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>체크아웃 진입</t>
+        </is>
+      </c>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>체크아웃 진입 예외 처리</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?checkOut` 호출</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:141</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TS-FN-009-B1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FN-009</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>체크아웃 진입</t>
+        </is>
+      </c>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>체크아웃 진입 경계 조건</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?checkOut` 호출</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:141</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TS-FN-010-N1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FN-010</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>장바구니에서 품목 제거</t>
+        </is>
+      </c>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>장바구니에서 품목 제거 정상 처리</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?removeItemFromCart` 호출</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L47"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:94</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TS-FN-010-E1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FN-010</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>장바구니에서 품목 제거</t>
+        </is>
+      </c>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>장바구니에서 품목 제거 예외 처리</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?removeItemFromCart` 호출</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:94</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TS-FN-010-B1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FN-010</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>장바구니에서 품목 제거</t>
+        </is>
+      </c>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>장바구니에서 품목 제거 경계 조건</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?removeItemFromCart` 호출</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:94</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TS-FN-011-N1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FN-011</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>장바구니 수량 갱신</t>
+        </is>
+      </c>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>장바구니 수량 갱신 정상 처리</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?updateCartQuantities` 호출</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L50"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:116</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TS-FN-011-E1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FN-011</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>장바구니 수량 갱신</t>
+        </is>
+      </c>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>장바구니 수량 갱신 예외 처리</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?updateCartQuantities` 호출</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:116</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TS-FN-011-B1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FN-011</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>장바구니 수량 갱신</t>
+        </is>
+      </c>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>장바구니 수량 갱신 경계 조건</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?updateCartQuantities` 호출</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:116</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TS-FN-012-N1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FN-012</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>장바구니 조회</t>
+        </is>
+      </c>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>장바구니 조회 정상 처리</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?viewCart` 호출</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L53"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:137</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TS-FN-012-E1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FN-012</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>장바구니 조회</t>
+        </is>
+      </c>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>장바구니 조회 예외 처리</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?viewCart` 호출</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:137</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TS-FN-012-B1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FN-012</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>장바구니 조회</t>
+        </is>
+      </c>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>장바구니 조회 경계 조건</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Cart.action?viewCart` 호출</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CartActionBean.java:137</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TS-FN-013-N1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FN-013</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>카탈로그 메인 화면</t>
+        </is>
+      </c>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>카탈로그 메인 화면 정상 처리</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action` 호출</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L56"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:143</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TS-FN-013-E1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FN-013</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>카탈로그 메인 화면</t>
+        </is>
+      </c>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>카탈로그 메인 화면 예외 처리</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action` 호출</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:143</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TS-FN-013-B1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FN-013</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>카탈로그 메인 화면</t>
+        </is>
+      </c>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>카탈로그 메인 화면 경계 조건</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action` 호출</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:143</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TS-FN-014-N1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FN-014</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>상품 검색</t>
+        </is>
+      </c>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>상품 검색 정상 처리</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?searchProducts` 호출</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: PRODUCT(R)</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L59"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:190</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TS-FN-014-E1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FN-014</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>상품 검색</t>
+        </is>
+      </c>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>상품 검색 예외 처리</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?searchProducts` 호출</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:190</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TS-FN-014-B1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FN-014</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>상품 검색</t>
+        </is>
+      </c>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>상품 검색 경계 조건</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): PRODUCT(R)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?searchProducts` 호출</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L61"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:190</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TS-FN-015-N1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FN-015</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>카테고리 조회</t>
+        </is>
+      </c>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>카테고리 조회 정상 처리</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewCategory` 호출</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: CATEGORY(R) · PRODUCT(R)</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L62"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:153</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TS-FN-015-E1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FN-015</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>카테고리 조회</t>
+        </is>
+      </c>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>카테고리 조회 예외 처리</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewCategory` 호출</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:153</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TS-FN-015-B1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FN-015</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>카테고리 조회</t>
+        </is>
+      </c>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>카테고리 조회 경계 조건</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): CATEGORY(R) · PRODUCT(R)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewCategory` 호출</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L64"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:153</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TS-FN-016-N1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FN-016</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>품목 상세 조회</t>
+        </is>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>품목 상세 조회 정상 처리</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewItem` 호출</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R)</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L65"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:179</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TS-FN-016-E1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FN-016</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>품목 상세 조회</t>
+        </is>
+      </c>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>품목 상세 조회 예외 처리</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewItem` 호출</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:179</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TS-FN-016-B1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FN-016</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>품목 상세 조회</t>
+        </is>
+      </c>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>품목 상세 조회 경계 조건</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewItem` 호출</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L67"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:179</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TS-FN-017-N1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FN-017</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>상품 상세 조회</t>
+        </is>
+      </c>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>상품 상세 조회 정상 처리</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewProduct` 호출</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R) · PRODUCT(R)</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L68"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:166</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TS-FN-017-E1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FN-017</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>상품 상세 조회</t>
+        </is>
+      </c>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>상품 상세 조회 예외 처리</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewProduct` 호출</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:166</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TS-FN-017-B1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FN-017</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>상품 상세 조회</t>
+        </is>
+      </c>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>상품 상세 조회 경계 조건</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R) · PRODUCT(R)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Catalog.action?viewProduct` 호출</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L70"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/CatalogActionBean.java:166</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TS-FN-018-N1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FN-018</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>주문 목록 조회</t>
+        </is>
+      </c>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>주문 목록 조회 정상 처리</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?listOrders` 호출</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ORDERS(CR) · ORDERSTATUS(CR)</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L71"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:107</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TS-FN-018-E1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FN-018</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>주문 목록 조회</t>
+        </is>
+      </c>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>주문 목록 조회 예외 처리</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?listOrders` 호출</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:107</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TS-FN-018-B1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FN-018</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>주문 목록 조회</t>
+        </is>
+      </c>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>주문 목록 조회 경계 조건</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): ORDERS(CR) · ORDERSTATUS(CR)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?listOrders` 호출</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L73"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:107</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TS-FN-019-N1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FN-019</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>주문 생성</t>
+        </is>
+      </c>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>주문 생성 정상 처리</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?newOrder` 호출</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR) · SEQUENCE(RU)</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L74"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:142</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TS-FN-019-E1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FN-019</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>주문 생성</t>
+        </is>
+      </c>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>주문 생성 예외 처리</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?newOrder` 호출</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:142</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TS-FN-019-B1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FN-019</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>주문 생성</t>
+        </is>
+      </c>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>주문 생성 경계 조건</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR) · SEQUENCE(RU)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?newOrder` 호출</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L76"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:142</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TS-FN-020-N1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FN-020</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>주문 폼 표시</t>
+        </is>
+      </c>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>주문 폼 표시 정상 처리</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?newOrderForm` 호출</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L77"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:119</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TS-FN-020-E1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FN-020</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>주문 폼 표시</t>
+        </is>
+      </c>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>주문 폼 표시 예외 처리</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?newOrderForm` 호출</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:119</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TS-FN-020-B1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FN-020</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>주문 폼 표시</t>
+        </is>
+      </c>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>주문 폼 표시 경계 조건</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?newOrderForm` 호출</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:119</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TS-FN-021-N1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FN-021</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>주문 상세 조회</t>
+        </is>
+      </c>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>주문 상세 조회 정상 처리</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?viewOrder` 호출</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR)</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L80"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:171</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TS-FN-021-E1</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FN-021</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>주문 상세 조회</t>
+        </is>
+      </c>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>주문 상세 조회 예외 처리</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?viewOrder` 호출</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:171</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TS-FN-021-B1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>FN-021</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>주문 상세 조회</t>
+        </is>
+      </c>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>주문 상세 조회 경계 조건</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>`ANY /actions/Order.action?viewOrder` 호출</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L82"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>src/main/java/org/mybatis/jpetstore/web/actions/OrderActionBean.java:171</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TS-FN-022-N1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FN-022</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>*.action 요청 라우팅 흐름</t>
+        </is>
+      </c>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>*.action 요청 라우팅 흐름 정상 처리</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>유효한 입력과 선행 상태가 준비됨</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>`ANY *.action` 호출</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>정상 완료(오류 없음) + 응답/결과 확인</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L83"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>src/main/webapp/WEB-INF/web.xml:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TS-FN-022-E1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>FN-022</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>*.action 요청 라우팅 흐름</t>
+        </is>
+      </c>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>예외</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>*.action 요청 라우팅 흐름 예외 처리</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>필수 입력 누락 또는 부적합한 입력</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>`ANY *.action` 호출</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>오류를 안전하게 처리(비정상 종료·데이터 오염 없음) + 명확한 오류 응답 확인</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>[미확인] 예외 AC 없음 — 일반형 초안(사람 보강)</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>src/main/webapp/WEB-INF/web.xml:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TS-FN-022-B1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>FN-022</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>*.action 요청 라우팅 흐름</t>
+        </is>
+      </c>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>경계</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>*.action 요청 라우팅 흐름 경계 조건</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>경계 입력(빈 값·최대 길이·한계치)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>`ANY *.action` 호출</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>경계에서도 일관 동작(오류 없이 처리 또는 명확한 거부)</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>초안 [추정]</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>[미확인] 데이터 근거 없음 — 경계값은 사람 특정</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>src/main/webapp/WEB-INF/web.xml:60</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M85"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1847,85 +6658,132 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gaps</t>
+          <t>scenarios</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>unimplemented</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>REQ-001, REQ-002</t>
-        </is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gaps</t>
+          <t>scenarios</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>orphanCode</t>
-        </is>
-      </c>
-      <c r="C17"/>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gaps</t>
+          <t>scenarios</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>byKind</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>flow:ANY *.action, flow:ANY /actions/Account.action, flow:ANY /actions/Account.action?editAccount, flow:ANY /actions/Account.action?editAccountForm, flow:ANY /actions/Account.action?newAccount, flow:ANY /actions/Account.action?newAccountForm, flow:ANY /actions/Account.action?signoff, flow:ANY /actions/Account.action?signon, flow:ANY /actions/Cart.action?addItemToCart, flow:ANY /actions/Cart.action?checkOut, flow:ANY /actions/Cart.action?removeItemFromCart, flow:ANY /actions/Cart.action?updateCartQuantities, flow:ANY /actions/Cart.action?viewCart, flow:ANY /actions/Catalog.action, flow:ANY /actions/Catalog.action?searchProducts, flow:ANY /actions/Catalog.action?viewCategory, flow:ANY /actions/Catalog.action?viewItem, flow:ANY /actions/Catalog.action?viewProduct, flow:ANY /actions/Order.action?listOrders, flow:ANY /actions/Order.action?newOrder, flow:ANY /actions/Order.action?newOrderForm, flow:ANY /actions/Order.action?viewOrder</t>
+          <t>{"normal":28,"exception":28,"boundary":28}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>byRequirement</t>
+          <t>gaps</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>REQ-001</t>
+          <t>unimplemented</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"targetsTotal":6,"targetsBuilt":3,"acsTotal":6,"acsPassed":0}</t>
+          <t>REQ-001, REQ-002</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>gaps</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>orphanCode</t>
+        </is>
+      </c>
+      <c r="C20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>gaps</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>flow:ANY *.action, flow:ANY /actions/Account.action, flow:ANY /actions/Account.action?editAccount, flow:ANY /actions/Account.action?editAccountForm, flow:ANY /actions/Account.action?newAccount, flow:ANY /actions/Account.action?newAccountForm, flow:ANY /actions/Account.action?signoff, flow:ANY /actions/Account.action?signon, flow:ANY /actions/Cart.action?addItemToCart, flow:ANY /actions/Cart.action?checkOut, flow:ANY /actions/Cart.action?removeItemFromCart, flow:ANY /actions/Cart.action?updateCartQuantities, flow:ANY /actions/Cart.action?viewCart, flow:ANY /actions/Catalog.action, flow:ANY /actions/Catalog.action?searchProducts, flow:ANY /actions/Catalog.action?viewCategory, flow:ANY /actions/Catalog.action?viewItem, flow:ANY /actions/Catalog.action?viewProduct, flow:ANY /actions/Order.action?listOrders, flow:ANY /actions/Order.action?newOrder, flow:ANY /actions/Order.action?newOrderForm, flow:ANY /actions/Order.action?viewOrder</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>byRequirement</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{"targetsTotal":6,"targetsBuilt":3,"acsTotal":6,"acsPassed":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>byRequirement</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>REQ-002</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>{"targetsTotal":6,"targetsBuilt":3,"acsTotal":6,"acsPassed":0}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C20"/>
+  <autoFilter ref="A1:C23"/>
 </worksheet>
 </file>
--- a/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
@@ -1611,7 +1611,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="41" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -1696,7 +1696,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TS-FN-001-N1</t>
+          <t>TS-3653f930-N</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TS-FN-001-E1</t>
+          <t>TS-3653f930-E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1810,7 +1810,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TS-FN-001-B1</t>
+          <t>TS-3653f930-B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1869,7 +1869,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TS-FN-002-N1</t>
+          <t>TS-25737d9b-N</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TS-FN-002-E1</t>
+          <t>TS-25737d9b-E</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TS-FN-002-B1</t>
+          <t>TS-25737d9b-B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TS-FN-003-N1</t>
+          <t>TS-17db5e22-N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TS-FN-003-E1</t>
+          <t>TS-17db5e22-E</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2152,7 +2152,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TS-FN-003-B1</t>
+          <t>TS-17db5e22-B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2211,7 +2211,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TS-FN-004-N1</t>
+          <t>TS-eb7ff746-N</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2266,7 +2266,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TS-FN-004-E1</t>
+          <t>TS-eb7ff746-E</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2325,7 +2325,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TS-FN-004-B1</t>
+          <t>TS-eb7ff746-B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2380,7 +2380,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TS-FN-005-N1</t>
+          <t>TS-4c7a6412-N</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TS-FN-005-E1</t>
+          <t>TS-4c7a6412-E</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2494,7 +2494,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TS-FN-005-B1</t>
+          <t>TS-4c7a6412-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TS-FN-006-N1</t>
+          <t>TS-04cfd5f5-N</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2608,7 +2608,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TS-FN-006-E1</t>
+          <t>TS-04cfd5f5-E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TS-FN-006-B1</t>
+          <t>TS-04cfd5f5-B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2726,7 +2726,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TS-FN-007-N1</t>
+          <t>TS-8f388341-N</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TS-FN-007-E1</t>
+          <t>TS-8f388341-E</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2840,7 +2840,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TS-FN-007-B1</t>
+          <t>TS-8f388341-B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TS-FN-028-N1</t>
+          <t>TS-e64c2820-N</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TS-FN-028-E1</t>
+          <t>TS-e64c2820-E</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TS-FN-028-B1</t>
+          <t>TS-e64c2820-B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3052,7 +3052,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TS-FN-026-N1</t>
+          <t>TS-df20f8e4-N</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3103,7 +3103,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TS-FN-026-E1</t>
+          <t>TS-df20f8e4-E</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3158,7 +3158,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TS-FN-026-B1</t>
+          <t>TS-df20f8e4-B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3213,7 +3213,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TS-FN-027-N1</t>
+          <t>TS-c28dfd73-N</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TS-FN-027-E1</t>
+          <t>TS-c28dfd73-E:REQ-002:AC-4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TS-FN-027-B1</t>
+          <t>TS-c28dfd73-B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3374,7 +3374,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TS-FN-025-N1</t>
+          <t>TS-b853fe37-N</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TS-FN-025-E1</t>
+          <t>TS-b853fe37-E</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TS-FN-025-B1</t>
+          <t>TS-b853fe37-B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3531,7 +3531,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TS-FN-023-N1</t>
+          <t>TS-6eced6a8-N</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3582,7 +3582,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TS-FN-023-E1</t>
+          <t>TS-6eced6a8-E</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3637,7 +3637,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TS-FN-023-B1</t>
+          <t>TS-6eced6a8-B</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3692,7 +3692,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TS-FN-024-N1</t>
+          <t>TS-f4c305f8-N</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3743,7 +3743,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TS-FN-024-E1</t>
+          <t>TS-f4c305f8-E:REQ-001:AC-4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3802,7 +3802,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TS-FN-024-B1</t>
+          <t>TS-f4c305f8-B</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3853,7 +3853,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TS-FN-008-N1</t>
+          <t>TS-04f64890-N</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3908,7 +3908,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TS-FN-008-E1</t>
+          <t>TS-04f64890-E</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3967,7 +3967,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TS-FN-008-B1</t>
+          <t>TS-04f64890-B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4022,7 +4022,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TS-FN-009-N1</t>
+          <t>TS-8b59c03c-N</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TS-FN-009-E1</t>
+          <t>TS-8b59c03c-E</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4136,7 +4136,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TS-FN-009-B1</t>
+          <t>TS-8b59c03c-B</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4195,7 +4195,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TS-FN-010-N1</t>
+          <t>TS-c92c4cb9-N</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TS-FN-010-E1</t>
+          <t>TS-c92c4cb9-E</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TS-FN-010-B1</t>
+          <t>TS-c92c4cb9-B</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4368,7 +4368,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TS-FN-011-N1</t>
+          <t>TS-51f32dbf-N</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4423,7 +4423,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TS-FN-011-E1</t>
+          <t>TS-51f32dbf-E</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4482,7 +4482,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TS-FN-011-B1</t>
+          <t>TS-51f32dbf-B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4541,7 +4541,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TS-FN-012-N1</t>
+          <t>TS-0b6a73ab-N</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4596,7 +4596,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TS-FN-012-E1</t>
+          <t>TS-0b6a73ab-E</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4655,7 +4655,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TS-FN-012-B1</t>
+          <t>TS-0b6a73ab-B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TS-FN-013-N1</t>
+          <t>TS-d65a8766-N</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TS-FN-013-E1</t>
+          <t>TS-d65a8766-E</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TS-FN-013-B1</t>
+          <t>TS-d65a8766-B</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4887,7 +4887,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TS-FN-014-N1</t>
+          <t>TS-3e8d32ff-N</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TS-FN-014-E1</t>
+          <t>TS-3e8d32ff-E</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5001,7 +5001,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TS-FN-014-B1</t>
+          <t>TS-3e8d32ff-B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5056,7 +5056,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TS-FN-015-N1</t>
+          <t>TS-459d7e96-N</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5111,7 +5111,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TS-FN-015-E1</t>
+          <t>TS-459d7e96-E</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5170,7 +5170,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TS-FN-015-B1</t>
+          <t>TS-459d7e96-B</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5225,7 +5225,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TS-FN-016-N1</t>
+          <t>TS-477c47ac-N</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5280,7 +5280,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TS-FN-016-E1</t>
+          <t>TS-477c47ac-E</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5339,7 +5339,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TS-FN-016-B1</t>
+          <t>TS-477c47ac-B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5394,7 +5394,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TS-FN-017-N1</t>
+          <t>TS-767ad04a-N</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TS-FN-017-E1</t>
+          <t>TS-767ad04a-E</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5508,7 +5508,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TS-FN-017-B1</t>
+          <t>TS-767ad04a-B</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5563,7 +5563,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TS-FN-018-N1</t>
+          <t>TS-613f4894-N</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TS-FN-018-E1</t>
+          <t>TS-613f4894-E</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5677,7 +5677,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TS-FN-018-B1</t>
+          <t>TS-613f4894-B</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5732,7 +5732,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TS-FN-019-N1</t>
+          <t>TS-8eddc158-N</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5787,7 +5787,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TS-FN-019-E1</t>
+          <t>TS-8eddc158-E</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TS-FN-019-B1</t>
+          <t>TS-8eddc158-B</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5901,7 +5901,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TS-FN-020-N1</t>
+          <t>TS-a885b63f-N</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5956,7 +5956,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TS-FN-020-E1</t>
+          <t>TS-a885b63f-E</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6015,7 +6015,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TS-FN-020-B1</t>
+          <t>TS-a885b63f-B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6074,7 +6074,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TS-FN-021-N1</t>
+          <t>TS-d7a0601e-N</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6129,7 +6129,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TS-FN-021-E1</t>
+          <t>TS-d7a0601e-E</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6188,7 +6188,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TS-FN-021-B1</t>
+          <t>TS-d7a0601e-B</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6243,7 +6243,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TS-FN-022-N1</t>
+          <t>TS-ef87ef36-N</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6298,7 +6298,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TS-FN-022-E1</t>
+          <t>TS-ef87ef36-E</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TS-FN-022-B1</t>
+          <t>TS-ef87ef36-B</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">

--- a/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
@@ -1906,7 +1906,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(RU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(RU) · SIGNON(RU)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(RU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(RU) · SIGNON(RU)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CR) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CR) · SIGNON(CR)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CR) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CR) · SIGNON(CR)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ACCOUNT(R) · BANNERDATA(R) · PRODUCT(R) · PROFILE(R) · SIGNON(R)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(CRU) · BANNERDATA(R) · PRODUCT(R) · PROFILE(CRU) · SIGNON(CRU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ACCOUNT(R) · BANNERDATA(R) · PRODUCT(R) · PROFILE(R) · SIGNON(R)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ITEM(R)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ITEM(R)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R) · PRODUCT(R)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ITEM(R) · PRODUCT(R)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R) · PRODUCT(R)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ITEM(R) · PRODUCT(R)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR) · SEQUENCE(RU)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(U) · LINEITEM(C) · ORDERS(C) · ORDERSTATUS(C) · SEQUENCE(RU)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR) · SEQUENCE(RU)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(U) · LINEITEM(C) · ORDERS(C) · ORDERSTATUS(C) · SEQUENCE(RU)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>정상 완료(오류 없음) + 데이터 반영 확인: INVENTORY(R) · ITEM(R) · LINEITEM(R) · ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(RU) · ITEM(R) · LINEITEM(CR) · ORDERS(CR) · ORDERSTATUS(CR)</t>
+          <t>경계 데이터 상태(대상 0건·최대치): INVENTORY(R) · ITEM(R) · LINEITEM(R) · ORDERS(R) · ORDERSTATUS(R)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">

--- a/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/rtm.xlsx
@@ -109,7 +109,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>
